--- a/Statistics/Section 2 - Descriptive Statistics Fundamentals/10_Standard deviation and coefficient of variation/Exercises/2.10.Standard-deviation-and-coefficient-of-variation-exercise - completed.xlsx
+++ b/Statistics/Section 2 - Descriptive Statistics Fundamentals/10_Standard deviation and coefficient of variation/Exercises/2.10.Standard-deviation-and-coefficient-of-variation-exercise - completed.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\365 Data Science\Statistics\Section 2\10_Standard deviation and coefficient of variation\Exercises\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slong\365 Data Science\Statistics\Section 2 - Descriptive Statistics Fundamentals\10_Standard deviation and coefficient of variation_\Exercises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A416F4-520E-46FA-B33E-C2DDF15FBBA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263E80D6-DCF6-460F-BF55-14E6B51B3DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -547,7 +550,7 @@
     <col min="6" max="6" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="20.109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5546875" style="1" customWidth="1"/>
     <col min="10" max="10" width="5.33203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.109375" style="1" bestFit="1" customWidth="1"/>
